--- a/ConfigTools/Config/Datas/__tables__.xlsx
+++ b/ConfigTools/Config/Datas/__tables__.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="28.5833333333333" customWidth="1" style="4" min="2" max="2"/>
@@ -1285,7 +1285,7 @@
           <t>Bullet@Bullet.xlsx</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>BulletId</t>
         </is>
@@ -1311,7 +1311,7 @@
           <t>Buff@Buff.xlsx</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>BuffId</t>
         </is>
@@ -1337,9 +1337,129 @@
           <t>Item@Item.xlsx</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>ItemTypeId</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>TbRoguelikeEffect</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeEffectDef</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeEffect@RoguelikeEffect.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>EffectId</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>肉鸽效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>TbRoguelikeItem</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeItemDef</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeItem@RoguelikeItem.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>肉鸽商店道具</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>TbRoguelikeShopPool</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeShopPoolDef</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeShopPool@RoguelikeShopPool.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>PoolId</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>肉鸽商店池</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>TbRoguelikeLevel</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeLevelDef</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>RoguelikeLevel@RoguelikeLevel.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>BigLevelId+LevelId</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>肉鸽小关</t>
         </is>
       </c>
     </row>
